--- a/data/trans_camb/IP16A01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-40,34; -14,11</t>
+          <t>-42,0; -13,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-60,35; -25,64</t>
+          <t>-59,66; -25,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-49,66; -20,48</t>
+          <t>-49,37; -19,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-52,1; -24,15</t>
+          <t>-52,66; -24,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,35; -39,06</t>
+          <t>-71,0; -36,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,62; -17,12</t>
+          <t>-49,73; -15,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,07; -22,58</t>
+          <t>-42,69; -22,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,31; -36,1</t>
+          <t>-60,89; -35,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-44,07; -21,74</t>
+          <t>-44,17; -21,69</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,34; -14,11</t>
+          <t>-42,0; -13,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-60,35; -25,64</t>
+          <t>-59,66; -25,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,66; -20,48</t>
+          <t>-49,37; -19,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,1; -24,15</t>
+          <t>-52,66; -24,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,35; -39,06</t>
+          <t>-71,0; -36,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,62; -17,12</t>
+          <t>-49,73; -15,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,07; -22,58</t>
+          <t>-42,69; -22,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,31; -36,1</t>
+          <t>-60,89; -35,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-44,07; -21,74</t>
+          <t>-44,17; -21,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-52,59; -27,47</t>
+          <t>-51,24; -27,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-53,88; -29,99</t>
+          <t>-54,84; -31,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-67,01; -33,48</t>
+          <t>-67,92; -33,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-58,19; -31,56</t>
+          <t>-57,63; -31,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,39; -24,26</t>
+          <t>-49,28; -24,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,72; -33,1</t>
+          <t>-54,62; -32,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,94; -33,38</t>
+          <t>-51,08; -33,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,13; -30,59</t>
+          <t>-47,36; -30,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-56,8; -36,63</t>
+          <t>-56,68; -37,42</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,59; -27,47</t>
+          <t>-51,24; -27,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,88; -29,99</t>
+          <t>-54,84; -31,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,01; -33,48</t>
+          <t>-67,92; -33,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,19; -31,56</t>
+          <t>-57,63; -31,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,39; -24,26</t>
+          <t>-49,28; -24,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,72; -33,1</t>
+          <t>-54,62; -32,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,94; -33,38</t>
+          <t>-51,08; -33,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,13; -30,59</t>
+          <t>-47,36; -30,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,8; -36,63</t>
+          <t>-56,68; -37,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-49,46; -23,94</t>
+          <t>-49,91; -24,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-41,95; -16,67</t>
+          <t>-41,99; -16,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-70,92; -16,52</t>
+          <t>-71,22; -16,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-44,1; -19,26</t>
+          <t>-43,86; -19,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-67,23; -36,6</t>
+          <t>-66,49; -34,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-58,04; -32,88</t>
+          <t>-59,11; -32,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-41,49; -24,49</t>
+          <t>-42,32; -24,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-49,75; -29,04</t>
+          <t>-49,6; -29,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-58,58; -25,25</t>
+          <t>-58,42; -23,82</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,46; -23,94</t>
+          <t>-49,91; -24,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,95; -16,67</t>
+          <t>-41,99; -16,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,92; -16,52</t>
+          <t>-71,22; -16,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,1; -19,26</t>
+          <t>-43,86; -19,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,23; -36,6</t>
+          <t>-66,49; -34,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,04; -32,88</t>
+          <t>-59,11; -32,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,49; -24,49</t>
+          <t>-42,32; -24,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,75; -29,04</t>
+          <t>-49,6; -29,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-58,58; -25,25</t>
+          <t>-58,42; -23,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-42,07; -18,68</t>
+          <t>-42,3; -18,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-57,19; -28,13</t>
+          <t>-57,38; -27,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-47,22; -19,7</t>
+          <t>-47,18; -19,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-51,02; -27,21</t>
+          <t>-52,12; -26,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-59,78; -29,02</t>
+          <t>-58,25; -27,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-53,75; -25,61</t>
+          <t>-54,77; -25,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-42,38; -25,45</t>
+          <t>-43,28; -26,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-52,43; -31,78</t>
+          <t>-52,33; -31,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-46,78; -26,52</t>
+          <t>-46,81; -26,46</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,07; -18,68</t>
+          <t>-42,3; -18,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,19; -28,13</t>
+          <t>-57,38; -27,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,22; -19,7</t>
+          <t>-47,18; -19,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-51,02; -27,21</t>
+          <t>-52,12; -26,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,78; -29,02</t>
+          <t>-58,25; -27,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,75; -25,61</t>
+          <t>-54,77; -25,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,38; -25,45</t>
+          <t>-43,28; -26,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,43; -31,78</t>
+          <t>-52,33; -31,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-46,78; -26,52</t>
+          <t>-46,81; -26,46</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-39,3; -26,63</t>
+          <t>-39,58; -27,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-46,55; -32,0</t>
+          <t>-45,72; -31,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-51,3; -23,97</t>
+          <t>-52,04; -25,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-44,12; -31,68</t>
+          <t>-43,61; -31,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-52,45; -37,17</t>
+          <t>-52,05; -37,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-47,0; -33,48</t>
+          <t>-48,01; -34,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-39,59; -30,87</t>
+          <t>-39,75; -30,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-46,92; -36,87</t>
+          <t>-46,5; -36,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-47,14; -31,58</t>
+          <t>-47,48; -32,13</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,3; -26,63</t>
+          <t>-39,58; -27,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,55; -32,0</t>
+          <t>-45,72; -31,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,3; -23,97</t>
+          <t>-52,04; -25,12</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-44,12; -31,68</t>
+          <t>-43,61; -31,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,45; -37,17</t>
+          <t>-52,05; -37,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,0; -33,48</t>
+          <t>-48,01; -34,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-39,59; -30,87</t>
+          <t>-39,75; -30,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-46,92; -36,87</t>
+          <t>-46,5; -36,81</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-47,14; -31,58</t>
+          <t>-47,48; -32,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-42,0; -13,91</t>
+          <t>-38,73; -13,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-59,66; -25,39</t>
+          <t>-58,33; -24,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-49,37; -19,13</t>
+          <t>-50,74; -21,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-52,66; -24,37</t>
+          <t>-52,33; -24,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,0; -36,76</t>
+          <t>-73,45; -37,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,73; -15,99</t>
+          <t>-49,55; -17,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,69; -22,11</t>
+          <t>-41,6; -22,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,89; -35,87</t>
+          <t>-60,52; -35,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-44,17; -21,69</t>
+          <t>-44,35; -21,68</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,0; -13,91</t>
+          <t>-38,73; -13,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-59,66; -25,39</t>
+          <t>-58,33; -24,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,37; -19,13</t>
+          <t>-50,74; -21,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,66; -24,37</t>
+          <t>-52,33; -24,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,0; -36,76</t>
+          <t>-73,45; -37,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,73; -15,99</t>
+          <t>-49,55; -17,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,69; -22,11</t>
+          <t>-41,6; -22,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,89; -35,87</t>
+          <t>-60,52; -35,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-44,17; -21,69</t>
+          <t>-44,35; -21,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-51,24; -27,41</t>
+          <t>-52,18; -28,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-54,84; -31,35</t>
+          <t>-53,15; -29,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-67,92; -33,19</t>
+          <t>-68,71; -33,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-57,63; -31,67</t>
+          <t>-57,42; -30,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,28; -24,88</t>
+          <t>-48,01; -24,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,62; -32,4</t>
+          <t>-53,57; -31,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,08; -33,8</t>
+          <t>-51,03; -33,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,36; -30,89</t>
+          <t>-48,75; -30,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-56,68; -37,42</t>
+          <t>-55,55; -36,66</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,24; -27,41</t>
+          <t>-52,18; -28,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,84; -31,35</t>
+          <t>-53,15; -29,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,92; -33,19</t>
+          <t>-68,71; -33,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-57,63; -31,67</t>
+          <t>-57,42; -30,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,28; -24,88</t>
+          <t>-48,01; -24,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,62; -32,4</t>
+          <t>-53,57; -31,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,08; -33,8</t>
+          <t>-51,03; -33,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,36; -30,89</t>
+          <t>-48,75; -30,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,68; -37,42</t>
+          <t>-55,55; -36,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-49,91; -24,03</t>
+          <t>-50,9; -24,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-41,99; -16,1</t>
+          <t>-42,72; -16,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-71,22; -16,07</t>
+          <t>-70,93; -13,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-43,86; -19,55</t>
+          <t>-44,15; -19,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-66,49; -34,96</t>
+          <t>-67,11; -35,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,11; -32,41</t>
+          <t>-59,82; -32,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-42,32; -24,61</t>
+          <t>-41,88; -24,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-49,6; -29,81</t>
+          <t>-50,44; -30,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-58,42; -23,82</t>
+          <t>-58,5; -22,21</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,91; -24,03</t>
+          <t>-50,9; -24,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,99; -16,1</t>
+          <t>-42,72; -16,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,22; -16,07</t>
+          <t>-70,93; -13,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,86; -19,55</t>
+          <t>-44,15; -19,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,49; -34,96</t>
+          <t>-67,11; -35,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-59,11; -32,41</t>
+          <t>-59,82; -32,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,32; -24,61</t>
+          <t>-41,88; -24,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,6; -29,81</t>
+          <t>-50,44; -30,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-58,42; -23,82</t>
+          <t>-58,5; -22,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-42,3; -18,89</t>
+          <t>-41,84; -17,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-57,38; -27,64</t>
+          <t>-56,31; -27,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-47,18; -19,33</t>
+          <t>-45,72; -19,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-52,12; -26,53</t>
+          <t>-50,22; -26,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,25; -27,28</t>
+          <t>-56,93; -28,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-54,77; -25,45</t>
+          <t>-52,93; -24,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-43,28; -26,01</t>
+          <t>-42,59; -26,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-52,33; -31,87</t>
+          <t>-52,67; -32,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-46,81; -26,46</t>
+          <t>-45,98; -25,94</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,3; -18,89</t>
+          <t>-41,84; -17,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,38; -27,64</t>
+          <t>-56,31; -27,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,18; -19,33</t>
+          <t>-45,72; -19,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-52,12; -26,53</t>
+          <t>-50,22; -26,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,25; -27,28</t>
+          <t>-56,93; -28,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,77; -25,45</t>
+          <t>-52,93; -24,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,28; -26,01</t>
+          <t>-42,59; -26,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,33; -31,87</t>
+          <t>-52,67; -32,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-46,81; -26,46</t>
+          <t>-45,98; -25,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-39,58; -27,1</t>
+          <t>-38,83; -26,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-45,72; -31,55</t>
+          <t>-46,26; -31,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-52,04; -25,12</t>
+          <t>-51,72; -25,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-43,61; -31,13</t>
+          <t>-43,93; -30,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -37,33</t>
+          <t>-52,22; -37,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -34,16</t>
+          <t>-47,82; -34,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-39,75; -30,8</t>
+          <t>-40,34; -30,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-46,5; -36,81</t>
+          <t>-47,15; -37,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-47,48; -32,13</t>
+          <t>-46,8; -32,27</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,58; -27,1</t>
+          <t>-38,83; -26,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,72; -31,55</t>
+          <t>-46,26; -31,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-52,04; -25,12</t>
+          <t>-51,72; -25,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,61; -31,13</t>
+          <t>-43,93; -30,9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -37,33</t>
+          <t>-52,22; -37,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -34,16</t>
+          <t>-47,82; -34,11</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-39,75; -30,8</t>
+          <t>-40,34; -30,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-46,5; -36,81</t>
+          <t>-47,15; -37,11</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-47,48; -32,13</t>
+          <t>-46,8; -32,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-37,39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-56,24</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-28,01</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-25,31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-40,98</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-34,4</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-37,39</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-56,24</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-30,43</t>
+          <t>-33,72</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-32,35</t>
+          <t>-30,96</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-38,73; -13,67</t>
+          <t>-52,1; -24,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-58,33; -24,4</t>
+          <t>-74,35; -39,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-50,74; -21,35</t>
+          <t>-49,29; -15,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-52,33; -24,55</t>
+          <t>-40,34; -14,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,45; -37,96</t>
+          <t>-60,35; -25,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,55; -17,08</t>
+          <t>-49,4; -19,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,6; -22,81</t>
+          <t>-42,07; -22,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,52; -35,76</t>
+          <t>-60,31; -36,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-44,35; -21,68</t>
+          <t>-42,53; -21,05</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-37,39%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-56,24%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-28,01%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-25,31%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-40,98%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-34,4%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-37,39%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-56,24%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-30,43%</t>
+          <t>-33,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-32,35%</t>
+          <t>-30,96%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,73; -13,67</t>
+          <t>-52,1; -24,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-58,33; -24,4</t>
+          <t>-74,35; -39,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,74; -21,35</t>
+          <t>-49,29; -15,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,33; -24,55</t>
+          <t>-40,34; -14,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,45; -37,96</t>
+          <t>-60,35; -25,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,55; -17,08</t>
+          <t>-49,4; -19,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,6; -22,81</t>
+          <t>-42,07; -22,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,52; -35,76</t>
+          <t>-60,31; -36,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-44,35; -21,68</t>
+          <t>-42,53; -21,05</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-44,27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-35,57</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-42,01</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-39,44</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-41,96</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-48,64</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-44,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-35,57</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-43,16</t>
+          <t>-41,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-45,41</t>
+          <t>-41,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-52,18; -28,06</t>
+          <t>-58,19; -31,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-53,15; -29,88</t>
+          <t>-48,39; -24,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-68,71; -33,41</t>
+          <t>-53,54; -31,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-57,42; -30,99</t>
+          <t>-52,59; -27,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -24,7</t>
+          <t>-53,88; -29,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,57; -31,92</t>
+          <t>-54,31; -29,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,03; -33,9</t>
+          <t>-51,94; -33,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,75; -30,9</t>
+          <t>-47,13; -30,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-55,55; -36,66</t>
+          <t>-49,89; -32,93</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-44,27%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-35,57%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-42,01%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-39,44%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-41,96%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-48,64%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-44,27%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-35,57%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-43,16%</t>
+          <t>-41,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-45,41%</t>
+          <t>-41,76%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,18; -28,06</t>
+          <t>-58,19; -31,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,15; -29,88</t>
+          <t>-48,39; -24,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,71; -33,41</t>
+          <t>-53,54; -31,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-57,42; -30,99</t>
+          <t>-52,59; -27,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -24,7</t>
+          <t>-53,88; -29,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,57; -31,92</t>
+          <t>-54,31; -29,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,03; -33,9</t>
+          <t>-51,94; -33,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,75; -30,9</t>
+          <t>-47,13; -30,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,55; -36,66</t>
+          <t>-49,89; -32,93</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-29,88</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-50,94</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-44,47</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-36,07</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-27,91</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-43,55</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-29,88</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-50,94</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-44,74</t>
+          <t>-61,45</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-44,06</t>
+          <t>-52,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-50,9; -24,62</t>
+          <t>-44,1; -19,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-42,72; -16,15</t>
+          <t>-67,23; -36,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-70,93; -13,53</t>
+          <t>-59,19; -32,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-44,15; -19,72</t>
+          <t>-49,46; -23,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-67,11; -35,74</t>
+          <t>-41,95; -16,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,82; -32,89</t>
+          <t>-73,13; -46,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-41,88; -24,56</t>
+          <t>-41,49; -24,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,44; -30,1</t>
+          <t>-49,75; -29,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-58,5; -22,21</t>
+          <t>-61,78; -42,59</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-29,88%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-50,94%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-44,47%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-36,07%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-27,91%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-43,55%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-29,88%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-50,94%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-44,74%</t>
+          <t>-61,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-44,06%</t>
+          <t>-52,83%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,9; -24,62</t>
+          <t>-44,1; -19,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,72; -16,15</t>
+          <t>-67,23; -36,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,93; -13,53</t>
+          <t>-59,19; -32,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,15; -19,72</t>
+          <t>-49,46; -23,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,11; -35,74</t>
+          <t>-41,95; -16,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-59,82; -32,89</t>
+          <t>-73,13; -46,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,88; -24,56</t>
+          <t>-41,49; -24,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,44; -30,1</t>
+          <t>-49,75; -29,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-58,5; -22,21</t>
+          <t>-61,78; -42,59</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-38,05</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-42,79</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-40,91</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-29,31</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-41,61</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-31,82</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-38,05</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-42,79</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-39,08</t>
+          <t>-33,53</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-35,63</t>
+          <t>-37,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-41,84; -17,33</t>
+          <t>-51,02; -27,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-56,31; -27,08</t>
+          <t>-59,78; -29,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-45,72; -19,8</t>
+          <t>-55,94; -26,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-50,22; -26,6</t>
+          <t>-42,07; -18,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-56,93; -28,45</t>
+          <t>-57,19; -28,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-52,93; -24,33</t>
+          <t>-48,81; -20,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-42,59; -26,07</t>
+          <t>-42,38; -25,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-52,67; -32,35</t>
+          <t>-52,43; -31,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-45,98; -25,94</t>
+          <t>-48,49; -27,85</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-38,05%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-42,79%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-40,91%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-29,31%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-41,61%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-31,82%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-38,05%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-42,79%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-39,08%</t>
+          <t>-33,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-35,63%</t>
+          <t>-37,33%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,84; -17,33</t>
+          <t>-51,02; -27,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,31; -27,08</t>
+          <t>-59,78; -29,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,72; -19,8</t>
+          <t>-55,94; -26,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,22; -26,6</t>
+          <t>-42,07; -18,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,93; -28,45</t>
+          <t>-57,19; -28,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,93; -24,33</t>
+          <t>-48,81; -20,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,59; -26,07</t>
+          <t>-42,38; -25,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,67; -32,35</t>
+          <t>-52,43; -31,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-45,98; -25,94</t>
+          <t>-48,49; -27,85</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-37,6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-44,86</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-40,49</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-32,77</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-38,64</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-41,47</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-37,6</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-44,86</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-40,97</t>
+          <t>-45,47</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-41,21</t>
+          <t>-42,8</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-38,83; -26,1</t>
+          <t>-44,12; -31,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-46,26; -31,83</t>
+          <t>-52,45; -37,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-51,72; -25,75</t>
+          <t>-46,67; -33,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-43,93; -30,9</t>
+          <t>-39,3; -26,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-52,22; -37,65</t>
+          <t>-46,55; -32,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-47,82; -34,11</t>
+          <t>-52,8; -38,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-40,34; -30,98</t>
+          <t>-39,59; -30,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-47,15; -37,11</t>
+          <t>-46,92; -36,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-46,8; -32,27</t>
+          <t>-47,6; -38,07</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-37,6%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-44,86%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-40,49%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-32,77%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-38,64%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-41,47%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-37,6%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-44,86%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-40,97%</t>
+          <t>-45,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-41,21%</t>
+          <t>-42,8%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-38,83; -26,1</t>
+          <t>-44,12; -31,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,26; -31,83</t>
+          <t>-52,45; -37,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,72; -25,75</t>
+          <t>-46,67; -33,11</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,93; -30,9</t>
+          <t>-39,3; -26,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,22; -37,65</t>
+          <t>-46,55; -32,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,82; -34,11</t>
+          <t>-52,8; -38,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,34; -30,98</t>
+          <t>-39,59; -30,87</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-47,15; -37,11</t>
+          <t>-46,92; -36,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-46,8; -32,27</t>
+          <t>-47,6; -38,07</t>
         </is>
       </c>
     </row>
